--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>37130.21</v>
+        <v>35854.46</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9467.5</v>
+        <v>9257.09</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>699.33</v>
+        <v>683.78</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>77887.3</v>
+        <v>76156.3</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6978.62</v>
+        <v>6777.5</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1268.84</v>
+        <v>1242.65</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>44895.23</v>
+        <v>44910.95</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>22129.67</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>22129.67</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7905.85</v>
+        <v>8109.27</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10882.75</v>
+        <v>11025.85</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7076.23</v>
+        <v>7154.89</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3199.19</v>
+        <v>3227.45</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>36649.98</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1159.67</v>
+        <v>1168.85</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>35478.74</v>
+        <v>35697.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -930,7 +930,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2490-79-CM26</t>
+          <t>4973-40-SE26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>61.202.016-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>44910.95</v>
+        <v>1573308.56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5482-80-CM26</t>
+          <t>2490-79-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -993,14 +993,18 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>22072.83</v>
+        <v>44910.95</v>
       </c>
     </row>
     <row r="10">
@@ -1067,7 +1071,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2701-207-CM26</t>
+          <t>5482-80-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1082,7 +1086,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,12 +1096,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1122,13 +1126,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8109.27</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2702-184-CM26</t>
+          <t>2701-207-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,7 +1147,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1183,13 +1187,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11025.85</v>
+        <v>8109.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>550716-4-CM26</t>
+          <t>2702-184-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,22 +1208,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1244,13 +1248,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7154.89</v>
+        <v>11025.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1495206-1-CM26</t>
+          <t>550716-4-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,22 +1269,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1305,13 +1309,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3227.45</v>
+        <v>7154.89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1477-108-CM26</t>
+          <t>1495206-1-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1336,12 +1340,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1366,13 +1370,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>36973.69</v>
+        <v>3227.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1186801-4-CM26</t>
+          <t>1477-108-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1387,7 +1391,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1401,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1427,13 +1431,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1168.85</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>772003-4-CM26</t>
+          <t>1186801-4-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,7 +1452,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,12 +1462,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1488,6 +1492,67 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
+        <v>1168.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>772003-4-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.979.930-5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>35697.47</v>
       </c>
     </row>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1058,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1119,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1180,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1241,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1302,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1363,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1424,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1485,7 +1537,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1546,7 +1602,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
